--- a/docs/table/报价测试数据/报价系统功能基础数据功能结构所需字段V3.xlsx
+++ b/docs/table/报价测试数据/报价系统功能基础数据功能结构所需字段V3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\docs\table\报价测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A8836F-7C7C-4FBC-85F1-447185C7E87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65109327-6759-45B6-A13D-ADEAC039D70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="912" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="840" windowWidth="28395" windowHeight="14640" tabRatio="912" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元素单价" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="145">
   <si>
     <t>客户名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -646,6 +646,10 @@
   </si>
   <si>
     <t>销售料号</t>
+  </si>
+  <si>
+    <t>外购件23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1559,7 +1563,7 @@
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H3" s="4">
         <v>1</v>
